--- a/kobo/professores_semana2_diagnostico.xlsx
+++ b/kobo/professores_semana2_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J170"/>
+  <dimension ref="A1:J271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2872,221 +2872,276 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>net_actors</t>
+          <t>net_nota</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Atores do território (NET_ACTORS)</t>
+          <t>Atores do território (NET_ACTORS). Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se a escola já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>net_nota</t>
+          <t>net_rel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se a escola já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria. Use "Adicionar" para registrar um ator por vez.</t>
+          <t>Q3.11. Para cada tipo de ator, qual é a relação atual da escola com ele?</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>table-list</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>select_one cat_ator</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>net_cat</t>
+          <t>net_rel_01</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Categoria do ator</t>
+          <t>Secretaria de Educação</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>net_nome</t>
+          <t>net_rel_02</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nome do ator (ex.: UBS Vila Nova)</t>
+          <t>Secretaria de Meio Ambiente</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>select_one sim_nao_nsabe</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>net_existe</t>
+          <t>net_rel_03</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Existe no território?</t>
+          <t>Defesa Civil</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>select_one nivel_rel</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>net_nivel</t>
+          <t>net_rel_04</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nível de relação</t>
+          <t>Secretaria de Saúde</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>net_contrib_atual</t>
+          <t>net_rel_05</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Contribuições atuais</t>
+          <t>Assistência Social</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>net_contrib_atual_outro</t>
+          <t>net_rel_06</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>selected(${net_contrib_atual}, 'outro')</t>
+          <t>Obras</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>net_contrib_pot</t>
+          <t>net_rel_07</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Contribuições potenciais</t>
+          <t>Bombeiros</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>net_contrib_pot_outro</t>
+          <t>net_rel_08</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>selected(${net_contrib_pot}, 'outro')</t>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>select_one sim_nao</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>net_prioridade</t>
+          <t>net_rel_09</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prioridade para fortalecimento (NET_PRIORITY_ACTORS) — é um ator prioritário a fortalecer?</t>
+          <t>Vigilância</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>select_one nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>net_rel_10</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Outro (poder público)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>q3_11</t>
+          <t>net_rel_11</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Q3.11. A escola sabe a quem contatar em uma emergência climática?</t>
+          <t>Universidade</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -3098,44 +3153,39 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>q3_12</t>
+          <t>net_rel_12</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Q3.12. Quais são esses contatos?</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>${q3_11}='sim'</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Instituto Federal</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>q3_13</t>
+          <t>net_rel_13</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Q3.13. Existe um procedimento de emergência definido para eventos climáticos?</t>
+          <t>Escola técnica</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -3147,583 +3197,2780 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>q3_14</t>
+          <t>net_rel_14</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Q3.14. Esse procedimento está documentado/formalizado?</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>${q3_13}='sim'</t>
+          <t>Centro de pesquisa</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>q3_15</t>
+          <t>net_rel_15</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Q3.15. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Museu</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>select_multiple canais</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>q3_16</t>
+          <t>net_rel_16</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Q3.16. Canais de comunicação da escola com a comunidade</t>
+          <t>Jardim botânico</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>q3_16_outro</t>
+          <t>net_rel_17</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>selected(${q3_16}, 'outro')</t>
+          <t>Outro (educação/ciência)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>select_one suficiente</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>q3_17</t>
+          <t>net_rel_18</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Q3.17. Esses canais seriam suficientes numa emergência?</t>
+          <t>Associação de moradores</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>q3_18</t>
+          <t>net_rel_19</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Q3.18. Algum grupo fica de fora desses canais de comunicação?</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>q3_19</t>
+          <t>net_rel_20</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Q3.19. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Cooperativa</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>q3_20</t>
+          <t>net_rel_21</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Q3.20. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Catadores</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>select_multiple barr_artic</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>q3_21</t>
+          <t>net_rel_22</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Q3.21. Barreiras para articular com atores do território</t>
+          <t>Movimentos sociais</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>q3_21_outro</t>
+          <t>net_rel_23</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>selected(${q3_21}, 'outro')</t>
+          <t>Coletivos</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>q3_22</t>
+          <t>net_rel_24</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Q3.22. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Grupos culturais</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>q3_23</t>
+          <t>net_rel_25</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Q3.23. Quem participou desse caso?</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Organizações comunitárias/religiosas</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>q3_24</t>
+          <t>net_rel_26</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Q3.24. O que funcionou bem?</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Outro (sociedade civil)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>q3_25</t>
+          <t>net_rel_27</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Q3.25. Quais foram as dificuldades?</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Povos indígenas</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>q3_26</t>
+          <t>net_rel_28</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Q3.26. O que essa experiência ensinou?</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>${q3_22} != ''</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Quilombolas</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>q3_27</t>
+          <t>net_rel_29</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Q3.27. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Agricultores familiares</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>q3_28</t>
+          <t>net_rel_30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Q3.28. Por quê?</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>${q3_27} != ''</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Pescadores</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>evid_e3</t>
+          <t>net_rel_31</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Evidências — Evidências sobre participação e redes</t>
+          <t>Comunidades tradicionais</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>evid_e3_nota</t>
+          <t>net_rel_32</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+          <t>Lideranças</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>select_one tipo_evid</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>evid_e3_tipo</t>
+          <t>net_rel_33</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tipo de evidência</t>
+          <t>Detentores de conhecimentos locais</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>evid_e3_tipo_outro</t>
+          <t>net_rel_34</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>${evid_e3_tipo}='outro'</t>
+          <t>Outro (comunidades e conhecimentos)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>evid_e3_desc</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Descreva a evidência</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>evid_e3_anexo</t>
+          <t>net_atual</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Anexo (foto/documento) — opcional</t>
+          <t>Q3.12. Contribuições atuais — o que cada ator parceiro(a) já oferece à escola?</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>(${net_rel_01} = 'parceria' or ${net_rel_01} = 'articulacao') or (${net_rel_02} = 'parceria' or ${net_rel_02} = 'articulacao') or (${net_rel_03} = 'parceria' or ${net_rel_03} = 'articulacao') or (${net_rel_04} = 'parceria' or ${net_rel_04} = 'articulacao') or (${net_rel_05} = 'parceria' or ${net_rel_05} = 'articulacao') or (${net_rel_06} = 'parceria' or ${net_rel_06} = 'articulacao') or (${net_rel_07} = 'parceria' or ${net_rel_07} = 'articulacao') or (${net_rel_08} = 'parceria' or ${net_rel_08} = 'articulacao') or (${net_rel_09} = 'parceria' or ${net_rel_09} = 'articulacao') or (${net_rel_10} = 'parceria' or ${net_rel_10} = 'articulacao') or (${net_rel_11} = 'parceria' or ${net_rel_11} = 'articulacao') or (${net_rel_12} = 'parceria' or ${net_rel_12} = 'articulacao') or (${net_rel_13} = 'parceria' or ${net_rel_13} = 'articulacao') or (${net_rel_14} = 'parceria' or ${net_rel_14} = 'articulacao') or (${net_rel_15} = 'parceria' or ${net_rel_15} = 'articulacao') or (${net_rel_16} = 'parceria' or ${net_rel_16} = 'articulacao') or (${net_rel_17} = 'parceria' or ${net_rel_17} = 'articulacao') or (${net_rel_18} = 'parceria' or ${net_rel_18} = 'articulacao') or (${net_rel_19} = 'parceria' or ${net_rel_19} = 'articulacao') or (${net_rel_20} = 'parceria' or ${net_rel_20} = 'articulacao') or (${net_rel_21} = 'parceria' or ${net_rel_21} = 'articulacao') or (${net_rel_22} = 'parceria' or ${net_rel_22} = 'articulacao') or (${net_rel_23} = 'parceria' or ${net_rel_23} = 'articulacao') or (${net_rel_24} = 'parceria' or ${net_rel_24} = 'articulacao') or (${net_rel_25} = 'parceria' or ${net_rel_25} = 'articulacao') or (${net_rel_26} = 'parceria' or ${net_rel_26} = 'articulacao') or (${net_rel_27} = 'parceria' or ${net_rel_27} = 'articulacao') or (${net_rel_28} = 'parceria' or ${net_rel_28} = 'articulacao') or (${net_rel_29} = 'parceria' or ${net_rel_29} = 'articulacao') or (${net_rel_30} = 'parceria' or ${net_rel_30} = 'articulacao') or (${net_rel_31} = 'parceria' or ${net_rel_31} = 'articulacao') or (${net_rel_32} = 'parceria' or ${net_rel_32} = 'articulacao') or (${net_rel_33} = 'parceria' or ${net_rel_33} = 'articulacao') or (${net_rel_34} = 'parceria' or ${net_rel_34} = 'articulacao')</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>table-list</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>net_atual_01</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Secretaria de Educação</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>${net_rel_01} = 'parceria' or ${net_rel_01} = 'articulacao'</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>net_atual_02</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Secretaria de Meio Ambiente</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>${net_rel_02} = 'parceria' or ${net_rel_02} = 'articulacao'</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_multiple contrib</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>confirmacao</t>
+          <t>net_atual_03</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Confirmação final</t>
+          <t>Defesa Civil</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>${net_rel_03} = 'parceria' or ${net_rel_03} = 'articulacao'</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple contrib</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>confirmacao_msg</t>
+          <t>net_atual_04</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
+          <t>Secretaria de Saúde</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>${net_rel_04} = 'parceria' or ${net_rel_04} = 'articulacao'</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>select_one confirmo</t>
+          <t>select_multiple contrib</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>confirmacao_envio</t>
+          <t>net_atual_05</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Revisei minhas respostas e confirmo o envio.</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>Assistência Social</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>${net_rel_05} = 'parceria' or ${net_rel_05} = 'articulacao'</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>net_atual_06</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Obras</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>${net_rel_06} = 'parceria' or ${net_rel_06} = 'articulacao'</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>net_atual_07</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Bombeiros</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>${net_rel_07} = 'parceria' or ${net_rel_07} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>net_atual_08</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>${net_rel_08} = 'parceria' or ${net_rel_08} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>net_atual_09</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Vigilância</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>${net_rel_09} = 'parceria' or ${net_rel_09} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>net_atual_10</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Outro (poder público)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>${net_rel_10} = 'parceria' or ${net_rel_10} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>net_atual_11</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Universidade</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>${net_rel_11} = 'parceria' or ${net_rel_11} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>net_atual_12</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Instituto Federal</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>${net_rel_12} = 'parceria' or ${net_rel_12} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>net_atual_13</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Escola técnica</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>${net_rel_13} = 'parceria' or ${net_rel_13} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>net_atual_14</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Centro de pesquisa</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>${net_rel_14} = 'parceria' or ${net_rel_14} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>net_atual_15</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Museu</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>${net_rel_15} = 'parceria' or ${net_rel_15} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>net_atual_16</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Jardim botânico</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>${net_rel_16} = 'parceria' or ${net_rel_16} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>net_atual_17</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Outro (educação/ciência)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>${net_rel_17} = 'parceria' or ${net_rel_17} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>net_atual_18</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Associação de moradores</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>${net_rel_18} = 'parceria' or ${net_rel_18} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>net_atual_19</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>${net_rel_19} = 'parceria' or ${net_rel_19} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>net_atual_20</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Cooperativa</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>${net_rel_20} = 'parceria' or ${net_rel_20} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>net_atual_21</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Catadores</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>${net_rel_21} = 'parceria' or ${net_rel_21} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>net_atual_22</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Movimentos sociais</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>${net_rel_22} = 'parceria' or ${net_rel_22} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>net_atual_23</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Coletivos</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>${net_rel_23} = 'parceria' or ${net_rel_23} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>net_atual_24</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Grupos culturais</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>${net_rel_24} = 'parceria' or ${net_rel_24} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>net_atual_25</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Organizações comunitárias/religiosas</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>${net_rel_25} = 'parceria' or ${net_rel_25} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>net_atual_26</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Outro (sociedade civil)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>${net_rel_26} = 'parceria' or ${net_rel_26} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>net_atual_27</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Povos indígenas</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>${net_rel_27} = 'parceria' or ${net_rel_27} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>net_atual_28</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Quilombolas</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>${net_rel_28} = 'parceria' or ${net_rel_28} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>net_atual_29</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Agricultores familiares</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>${net_rel_29} = 'parceria' or ${net_rel_29} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>net_atual_30</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Pescadores</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>${net_rel_30} = 'parceria' or ${net_rel_30} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>net_atual_31</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Comunidades tradicionais</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>${net_rel_31} = 'parceria' or ${net_rel_31} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>net_atual_32</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Lideranças</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>${net_rel_32} = 'parceria' or ${net_rel_32} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>net_atual_33</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Detentores de conhecimentos locais</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>${net_rel_33} = 'parceria' or ${net_rel_33} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>net_atual_34</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Outro (comunidades e conhecimentos)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>${net_rel_34} = 'parceria' or ${net_rel_34} = 'articulacao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>net_atual_outro</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Especifique (Outro) — contribuições atuais</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>selected(${net_atual_01}, 'outro') or selected(${net_atual_02}, 'outro') or selected(${net_atual_03}, 'outro') or selected(${net_atual_04}, 'outro') or selected(${net_atual_05}, 'outro') or selected(${net_atual_06}, 'outro') or selected(${net_atual_07}, 'outro') or selected(${net_atual_08}, 'outro') or selected(${net_atual_09}, 'outro') or selected(${net_atual_10}, 'outro') or selected(${net_atual_11}, 'outro') or selected(${net_atual_12}, 'outro') or selected(${net_atual_13}, 'outro') or selected(${net_atual_14}, 'outro') or selected(${net_atual_15}, 'outro') or selected(${net_atual_16}, 'outro') or selected(${net_atual_17}, 'outro') or selected(${net_atual_18}, 'outro') or selected(${net_atual_19}, 'outro') or selected(${net_atual_20}, 'outro') or selected(${net_atual_21}, 'outro') or selected(${net_atual_22}, 'outro') or selected(${net_atual_23}, 'outro') or selected(${net_atual_24}, 'outro') or selected(${net_atual_25}, 'outro') or selected(${net_atual_26}, 'outro') or selected(${net_atual_27}, 'outro') or selected(${net_atual_28}, 'outro') or selected(${net_atual_29}, 'outro') or selected(${net_atual_30}, 'outro') or selected(${net_atual_31}, 'outro') or selected(${net_atual_32}, 'outro') or selected(${net_atual_33}, 'outro') or selected(${net_atual_34}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>net_pot</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Q3.13. Contribuições potenciais — o que cada ator que existe no território poderia oferecer?</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>(${net_rel_01} != '' and ${net_rel_01} != 'nao_existe' and ${net_rel_01} != 'nao_sei') or (${net_rel_02} != '' and ${net_rel_02} != 'nao_existe' and ${net_rel_02} != 'nao_sei') or (${net_rel_03} != '' and ${net_rel_03} != 'nao_existe' and ${net_rel_03} != 'nao_sei') or (${net_rel_04} != '' and ${net_rel_04} != 'nao_existe' and ${net_rel_04} != 'nao_sei') or (${net_rel_05} != '' and ${net_rel_05} != 'nao_existe' and ${net_rel_05} != 'nao_sei') or (${net_rel_06} != '' and ${net_rel_06} != 'nao_existe' and ${net_rel_06} != 'nao_sei') or (${net_rel_07} != '' and ${net_rel_07} != 'nao_existe' and ${net_rel_07} != 'nao_sei') or (${net_rel_08} != '' and ${net_rel_08} != 'nao_existe' and ${net_rel_08} != 'nao_sei') or (${net_rel_09} != '' and ${net_rel_09} != 'nao_existe' and ${net_rel_09} != 'nao_sei') or (${net_rel_10} != '' and ${net_rel_10} != 'nao_existe' and ${net_rel_10} != 'nao_sei') or (${net_rel_11} != '' and ${net_rel_11} != 'nao_existe' and ${net_rel_11} != 'nao_sei') or (${net_rel_12} != '' and ${net_rel_12} != 'nao_existe' and ${net_rel_12} != 'nao_sei') or (${net_rel_13} != '' and ${net_rel_13} != 'nao_existe' and ${net_rel_13} != 'nao_sei') or (${net_rel_14} != '' and ${net_rel_14} != 'nao_existe' and ${net_rel_14} != 'nao_sei') or (${net_rel_15} != '' and ${net_rel_15} != 'nao_existe' and ${net_rel_15} != 'nao_sei') or (${net_rel_16} != '' and ${net_rel_16} != 'nao_existe' and ${net_rel_16} != 'nao_sei') or (${net_rel_17} != '' and ${net_rel_17} != 'nao_existe' and ${net_rel_17} != 'nao_sei') or (${net_rel_18} != '' and ${net_rel_18} != 'nao_existe' and ${net_rel_18} != 'nao_sei') or (${net_rel_19} != '' and ${net_rel_19} != 'nao_existe' and ${net_rel_19} != 'nao_sei') or (${net_rel_20} != '' and ${net_rel_20} != 'nao_existe' and ${net_rel_20} != 'nao_sei') or (${net_rel_21} != '' and ${net_rel_21} != 'nao_existe' and ${net_rel_21} != 'nao_sei') or (${net_rel_22} != '' and ${net_rel_22} != 'nao_existe' and ${net_rel_22} != 'nao_sei') or (${net_rel_23} != '' and ${net_rel_23} != 'nao_existe' and ${net_rel_23} != 'nao_sei') or (${net_rel_24} != '' and ${net_rel_24} != 'nao_existe' and ${net_rel_24} != 'nao_sei') or (${net_rel_25} != '' and ${net_rel_25} != 'nao_existe' and ${net_rel_25} != 'nao_sei') or (${net_rel_26} != '' and ${net_rel_26} != 'nao_existe' and ${net_rel_26} != 'nao_sei') or (${net_rel_27} != '' and ${net_rel_27} != 'nao_existe' and ${net_rel_27} != 'nao_sei') or (${net_rel_28} != '' and ${net_rel_28} != 'nao_existe' and ${net_rel_28} != 'nao_sei') or (${net_rel_29} != '' and ${net_rel_29} != 'nao_existe' and ${net_rel_29} != 'nao_sei') or (${net_rel_30} != '' and ${net_rel_30} != 'nao_existe' and ${net_rel_30} != 'nao_sei') or (${net_rel_31} != '' and ${net_rel_31} != 'nao_existe' and ${net_rel_31} != 'nao_sei') or (${net_rel_32} != '' and ${net_rel_32} != 'nao_existe' and ${net_rel_32} != 'nao_sei') or (${net_rel_33} != '' and ${net_rel_33} != 'nao_existe' and ${net_rel_33} != 'nao_sei') or (${net_rel_34} != '' and ${net_rel_34} != 'nao_existe' and ${net_rel_34} != 'nao_sei')</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>table-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>net_pot_01</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Secretaria de Educação</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>${net_rel_01} != '' and ${net_rel_01} != 'nao_existe' and ${net_rel_01} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>net_pot_02</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Secretaria de Meio Ambiente</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>${net_rel_02} != '' and ${net_rel_02} != 'nao_existe' and ${net_rel_02} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>net_pot_03</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Defesa Civil</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>${net_rel_03} != '' and ${net_rel_03} != 'nao_existe' and ${net_rel_03} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>net_pot_04</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Secretaria de Saúde</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>${net_rel_04} != '' and ${net_rel_04} != 'nao_existe' and ${net_rel_04} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>net_pot_05</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Assistência Social</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>${net_rel_05} != '' and ${net_rel_05} != 'nao_existe' and ${net_rel_05} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>net_pot_06</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Obras</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>${net_rel_06} != '' and ${net_rel_06} != 'nao_existe' and ${net_rel_06} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>net_pot_07</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Bombeiros</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>${net_rel_07} != '' and ${net_rel_07} != 'nao_existe' and ${net_rel_07} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>net_pot_08</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>${net_rel_08} != '' and ${net_rel_08} != 'nao_existe' and ${net_rel_08} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>net_pot_09</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Vigilância</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>${net_rel_09} != '' and ${net_rel_09} != 'nao_existe' and ${net_rel_09} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>net_pot_10</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Outro (poder público)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>${net_rel_10} != '' and ${net_rel_10} != 'nao_existe' and ${net_rel_10} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>net_pot_11</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Universidade</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>${net_rel_11} != '' and ${net_rel_11} != 'nao_existe' and ${net_rel_11} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>net_pot_12</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Instituto Federal</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>${net_rel_12} != '' and ${net_rel_12} != 'nao_existe' and ${net_rel_12} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>net_pot_13</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Escola técnica</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>${net_rel_13} != '' and ${net_rel_13} != 'nao_existe' and ${net_rel_13} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>net_pot_14</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Centro de pesquisa</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>${net_rel_14} != '' and ${net_rel_14} != 'nao_existe' and ${net_rel_14} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>net_pot_15</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Museu</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>${net_rel_15} != '' and ${net_rel_15} != 'nao_existe' and ${net_rel_15} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>net_pot_16</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Jardim botânico</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>${net_rel_16} != '' and ${net_rel_16} != 'nao_existe' and ${net_rel_16} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>net_pot_17</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Outro (educação/ciência)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>${net_rel_17} != '' and ${net_rel_17} != 'nao_existe' and ${net_rel_17} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>net_pot_18</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Associação de moradores</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>${net_rel_18} != '' and ${net_rel_18} != 'nao_existe' and ${net_rel_18} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>net_pot_19</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>${net_rel_19} != '' and ${net_rel_19} != 'nao_existe' and ${net_rel_19} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>net_pot_20</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Cooperativa</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>${net_rel_20} != '' and ${net_rel_20} != 'nao_existe' and ${net_rel_20} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>net_pot_21</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Catadores</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>${net_rel_21} != '' and ${net_rel_21} != 'nao_existe' and ${net_rel_21} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>net_pot_22</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Movimentos sociais</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>${net_rel_22} != '' and ${net_rel_22} != 'nao_existe' and ${net_rel_22} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>net_pot_23</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Coletivos</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>${net_rel_23} != '' and ${net_rel_23} != 'nao_existe' and ${net_rel_23} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>net_pot_24</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Grupos culturais</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>${net_rel_24} != '' and ${net_rel_24} != 'nao_existe' and ${net_rel_24} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>net_pot_25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Organizações comunitárias/religiosas</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>${net_rel_25} != '' and ${net_rel_25} != 'nao_existe' and ${net_rel_25} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>net_pot_26</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Outro (sociedade civil)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>${net_rel_26} != '' and ${net_rel_26} != 'nao_existe' and ${net_rel_26} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>net_pot_27</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Povos indígenas</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>${net_rel_27} != '' and ${net_rel_27} != 'nao_existe' and ${net_rel_27} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>net_pot_28</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Quilombolas</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>${net_rel_28} != '' and ${net_rel_28} != 'nao_existe' and ${net_rel_28} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>net_pot_29</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Agricultores familiares</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>${net_rel_29} != '' and ${net_rel_29} != 'nao_existe' and ${net_rel_29} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>net_pot_30</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Pescadores</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>${net_rel_30} != '' and ${net_rel_30} != 'nao_existe' and ${net_rel_30} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>net_pot_31</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Comunidades tradicionais</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>${net_rel_31} != '' and ${net_rel_31} != 'nao_existe' and ${net_rel_31} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>net_pot_32</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Lideranças</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>${net_rel_32} != '' and ${net_rel_32} != 'nao_existe' and ${net_rel_32} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>net_pot_33</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Detentores de conhecimentos locais</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>${net_rel_33} != '' and ${net_rel_33} != 'nao_existe' and ${net_rel_33} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>select_multiple contrib</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>net_pot_34</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Outro (comunidades e conhecimentos)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>${net_rel_34} != '' and ${net_rel_34} != 'nao_existe' and ${net_rel_34} != 'nao_sei'</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>net_pot_outro</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Especifique (Outro) — contribuições potenciais</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>selected(${net_pot_01}, 'outro') or selected(${net_pot_02}, 'outro') or selected(${net_pot_03}, 'outro') or selected(${net_pot_04}, 'outro') or selected(${net_pot_05}, 'outro') or selected(${net_pot_06}, 'outro') or selected(${net_pot_07}, 'outro') or selected(${net_pot_08}, 'outro') or selected(${net_pot_09}, 'outro') or selected(${net_pot_10}, 'outro') or selected(${net_pot_11}, 'outro') or selected(${net_pot_12}, 'outro') or selected(${net_pot_13}, 'outro') or selected(${net_pot_14}, 'outro') or selected(${net_pot_15}, 'outro') or selected(${net_pot_16}, 'outro') or selected(${net_pot_17}, 'outro') or selected(${net_pot_18}, 'outro') or selected(${net_pot_19}, 'outro') or selected(${net_pot_20}, 'outro') or selected(${net_pot_21}, 'outro') or selected(${net_pot_22}, 'outro') or selected(${net_pot_23}, 'outro') or selected(${net_pot_24}, 'outro') or selected(${net_pot_25}, 'outro') or selected(${net_pot_26}, 'outro') or selected(${net_pot_27}, 'outro') or selected(${net_pot_28}, 'outro') or selected(${net_pot_29}, 'outro') or selected(${net_pot_30}, 'outro') or selected(${net_pot_31}, 'outro') or selected(${net_pot_32}, 'outro') or selected(${net_pot_33}, 'outro') or selected(${net_pot_34}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>select_multiple cat_ator</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>q3_14</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Q3.14. Quais atores são prioritários para fortalecer a relação? (NET_PRIORITY_ACTORS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>q3_15</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Q3.15. Cite o nome do ator mais relevante para a escola hoje (ex.: UBS Vila Nova)</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>select_one sim_nao_ns</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>q3_16</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Q3.16. A escola sabe a quem contatar em uma emergência climática?</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>q3_17</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Q3.17. Quais são esses contatos?</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>${q3_16}='sim'</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>select_one sim_nao_ns</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>q3_18</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Q3.18. Existe um procedimento de emergência definido para eventos climáticos?</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>select_one sim_nao_ns</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>q3_19</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Q3.19. Esse procedimento está documentado/formalizado?</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>${q3_18}='sim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>q3_20</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Q3.20. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>select_multiple canais</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>q3_21</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Q3.21. Canais de comunicação da escola com a comunidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>q3_21_outro</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>selected(${q3_21}, 'outro')</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>select_one suficiente</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>q3_22</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Q3.22. Esses canais seriam suficientes numa emergência?</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>q3_23</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Q3.23. Algum grupo fica de fora desses canais de comunicação?</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>q3_24</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Q3.24. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>q3_25</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Q3.25. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>select_multiple barr_artic</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>q3_26</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Q3.26. Barreiras para articular com atores do território</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>q3_26_outro</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>selected(${q3_26}, 'outro')</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>q3_27</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Q3.27. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>q3_28</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Q3.28. Quem participou desse caso?</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>q3_29</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Q3.29. O que funcionou bem?</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>q3_30</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Q3.30. Quais foram as dificuldades?</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>q3_31</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Q3.31. O que essa experiência ensinou?</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>${q3_27} != ''</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>q3_32</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Q3.32. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>q3_33</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Q3.33. Por quê?</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>${q3_32} != ''</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>begin_repeat</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>evid_e3</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Evidências — Evidências sobre participação e redes</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>evid_e3_nota</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>select_one tipo_evid</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>evid_e3_tipo</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Tipo de evidência</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>evid_e3_tipo_outro</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>${evid_e3_tipo}='outro'</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>evid_e3_desc</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Descreva a evidência</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>evid_e3_anexo</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Anexo (foto/documento) — opcional</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>end_repeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>confirmacao</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Confirmação final</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>confirmacao_msg</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>select_one confirmo</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>confirmacao_envio</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
@@ -3740,7 +5987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C265"/>
+  <dimension ref="A1:C266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7792,85 +10039,85 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Não existe relação — não é parceiro(a)</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>sabe_existe</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Sabe que existe, mas nunca houve contato — não é parceiro(a)</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Já houve contato pontual, sem combinação formal — ainda não é parceiro(a)</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>apoio_tecnico</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Apoio técnico</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>nivel_rel</t>
+          <t>contrib</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
@@ -7882,12 +10129,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>conhecimentos_tradicionais_locai</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Conhecimentos tradicionais/locais</t>
         </is>
       </c>
     </row>
@@ -7899,97 +10146,97 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>apoio_tecnico</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Apoio técnico</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>conhecimentos_tradicionais_locai</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Conhecimentos tradicionais/locais</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
@@ -8001,250 +10248,267 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>articulacao</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>

--- a/kobo/professores_semana2_diagnostico.xlsx
+++ b/kobo/professores_semana2_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J271"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3666,2311 +3666,693 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_multiple cat_ator</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>net_atual</t>
+          <t>q3_12</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Q3.12. Contribuições atuais — o que cada ator parceiro(a) já oferece à escola?</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>(${net_rel_01} = 'parceria' or ${net_rel_01} = 'articulacao') or (${net_rel_02} = 'parceria' or ${net_rel_02} = 'articulacao') or (${net_rel_03} = 'parceria' or ${net_rel_03} = 'articulacao') or (${net_rel_04} = 'parceria' or ${net_rel_04} = 'articulacao') or (${net_rel_05} = 'parceria' or ${net_rel_05} = 'articulacao') or (${net_rel_06} = 'parceria' or ${net_rel_06} = 'articulacao') or (${net_rel_07} = 'parceria' or ${net_rel_07} = 'articulacao') or (${net_rel_08} = 'parceria' or ${net_rel_08} = 'articulacao') or (${net_rel_09} = 'parceria' or ${net_rel_09} = 'articulacao') or (${net_rel_10} = 'parceria' or ${net_rel_10} = 'articulacao') or (${net_rel_11} = 'parceria' or ${net_rel_11} = 'articulacao') or (${net_rel_12} = 'parceria' or ${net_rel_12} = 'articulacao') or (${net_rel_13} = 'parceria' or ${net_rel_13} = 'articulacao') or (${net_rel_14} = 'parceria' or ${net_rel_14} = 'articulacao') or (${net_rel_15} = 'parceria' or ${net_rel_15} = 'articulacao') or (${net_rel_16} = 'parceria' or ${net_rel_16} = 'articulacao') or (${net_rel_17} = 'parceria' or ${net_rel_17} = 'articulacao') or (${net_rel_18} = 'parceria' or ${net_rel_18} = 'articulacao') or (${net_rel_19} = 'parceria' or ${net_rel_19} = 'articulacao') or (${net_rel_20} = 'parceria' or ${net_rel_20} = 'articulacao') or (${net_rel_21} = 'parceria' or ${net_rel_21} = 'articulacao') or (${net_rel_22} = 'parceria' or ${net_rel_22} = 'articulacao') or (${net_rel_23} = 'parceria' or ${net_rel_23} = 'articulacao') or (${net_rel_24} = 'parceria' or ${net_rel_24} = 'articulacao') or (${net_rel_25} = 'parceria' or ${net_rel_25} = 'articulacao') or (${net_rel_26} = 'parceria' or ${net_rel_26} = 'articulacao') or (${net_rel_27} = 'parceria' or ${net_rel_27} = 'articulacao') or (${net_rel_28} = 'parceria' or ${net_rel_28} = 'articulacao') or (${net_rel_29} = 'parceria' or ${net_rel_29} = 'articulacao') or (${net_rel_30} = 'parceria' or ${net_rel_30} = 'articulacao') or (${net_rel_31} = 'parceria' or ${net_rel_31} = 'articulacao') or (${net_rel_32} = 'parceria' or ${net_rel_32} = 'articulacao') or (${net_rel_33} = 'parceria' or ${net_rel_33} = 'articulacao') or (${net_rel_34} = 'parceria' or ${net_rel_34} = 'articulacao')</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>table-list</t>
+          <t>Q3.12. Quais atores são prioritários para fortalecer a relação? (NET_PRIORITY_ACTORS)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>net_atual_01</t>
+          <t>q3_13</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>${net_rel_01} = 'parceria' or ${net_rel_01} = 'articulacao'</t>
+          <t>Q3.13. Cite o nome do ator mais relevante para a escola hoje (ex.: UBS Vila Nova)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>net_atual_02</t>
+          <t>q3_14</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>${net_rel_02} = 'parceria' or ${net_rel_02} = 'articulacao'</t>
+          <t>Q3.14. A escola sabe a quem contatar em uma emergência climática?</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>net_atual_03</t>
+          <t>q3_15</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Q3.15. Quais são esses contatos?</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>${net_rel_03} = 'parceria' or ${net_rel_03} = 'articulacao'</t>
+          <t>${q3_14}='sim'</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>net_atual_04</t>
+          <t>q3_16</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>${net_rel_04} = 'parceria' or ${net_rel_04} = 'articulacao'</t>
+          <t>Q3.16. Existe um procedimento de emergência definido para eventos climáticos?</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>net_atual_05</t>
+          <t>q3_17</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Q3.17. Esse procedimento está documentado/formalizado?</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>${net_rel_05} = 'parceria' or ${net_rel_05} = 'articulacao'</t>
+          <t>${q3_16}='sim'</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>net_atual_06</t>
+          <t>q3_18</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Obras</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>${net_rel_06} = 'parceria' or ${net_rel_06} = 'articulacao'</t>
+          <t>Q3.18. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_multiple canais</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>net_atual_07</t>
+          <t>q3_19</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>${net_rel_07} = 'parceria' or ${net_rel_07} = 'articulacao'</t>
+          <t>Q3.19. Canais de comunicação da escola com a comunidade</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>net_atual_08</t>
+          <t>q3_19_outro</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>${net_rel_08} = 'parceria' or ${net_rel_08} = 'articulacao'</t>
+          <t>selected(${q3_19}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one suficiente</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>net_atual_09</t>
+          <t>q3_20</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Vigilância</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>${net_rel_09} = 'parceria' or ${net_rel_09} = 'articulacao'</t>
+          <t>Q3.20. Esses canais seriam suficientes numa emergência?</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>net_atual_10</t>
+          <t>q3_21</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>${net_rel_10} = 'parceria' or ${net_rel_10} = 'articulacao'</t>
+          <t>Q3.21. Algum grupo fica de fora desses canais de comunicação?</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>net_atual_11</t>
+          <t>q3_22</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Universidade</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>${net_rel_11} = 'parceria' or ${net_rel_11} = 'articulacao'</t>
+          <t>Q3.22. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>net_atual_12</t>
+          <t>q3_23</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>${net_rel_12} = 'parceria' or ${net_rel_12} = 'articulacao'</t>
+          <t>Q3.23. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_multiple barr_artic</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>net_atual_13</t>
+          <t>q3_24</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>${net_rel_13} = 'parceria' or ${net_rel_13} = 'articulacao'</t>
+          <t>Q3.24. Barreiras para articular com atores do território</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>net_atual_14</t>
+          <t>q3_24_outro</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>${net_rel_14} = 'parceria' or ${net_rel_14} = 'articulacao'</t>
+          <t>selected(${q3_24}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>net_atual_15</t>
+          <t>q3_25</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Museu</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>${net_rel_15} = 'parceria' or ${net_rel_15} = 'articulacao'</t>
+          <t>Q3.25. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>net_atual_16</t>
+          <t>q3_26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Q3.26. Quem participou desse caso?</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>${net_rel_16} = 'parceria' or ${net_rel_16} = 'articulacao'</t>
+          <t>${q3_25} != ''</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>net_atual_17</t>
+          <t>q3_27</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Q3.27. O que funcionou bem?</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>${net_rel_17} = 'parceria' or ${net_rel_17} = 'articulacao'</t>
+          <t>${q3_25} != ''</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>net_atual_18</t>
+          <t>q3_28</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Q3.28. Quais foram as dificuldades?</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>${net_rel_18} = 'parceria' or ${net_rel_18} = 'articulacao'</t>
+          <t>${q3_25} != ''</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>net_atual_19</t>
+          <t>q3_29</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Q3.29. O que essa experiência ensinou?</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>${net_rel_19} = 'parceria' or ${net_rel_19} = 'articulacao'</t>
+          <t>${q3_25} != ''</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>net_atual_20</t>
+          <t>q3_30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>${net_rel_20} = 'parceria' or ${net_rel_20} = 'articulacao'</t>
+          <t>Q3.30. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>net_atual_21</t>
+          <t>q3_31</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Q3.31. Por quê?</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>${net_rel_21} = 'parceria' or ${net_rel_21} = 'articulacao'</t>
+          <t>${q3_30} != ''</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>net_atual_22</t>
+          <t>evid_e3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>${net_rel_22} = 'parceria' or ${net_rel_22} = 'articulacao'</t>
+          <t>Evidências — Evidências sobre participação e redes</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>net_atual_23</t>
+          <t>evid_e3_nota</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Coletivos</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>${net_rel_23} = 'parceria' or ${net_rel_23} = 'articulacao'</t>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one tipo_evid</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>net_atual_24</t>
+          <t>evid_e3_tipo</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>${net_rel_24} = 'parceria' or ${net_rel_24} = 'articulacao'</t>
+          <t>Tipo de evidência</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>net_atual_25</t>
+          <t>evid_e3_tipo_outro</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>${net_rel_25} = 'parceria' or ${net_rel_25} = 'articulacao'</t>
+          <t>${evid_e3_tipo}='outro'</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>net_atual_26</t>
+          <t>evid_e3_desc</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>${net_rel_26} = 'parceria' or ${net_rel_26} = 'articulacao'</t>
+          <t>Descreva a evidência</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>net_atual_27</t>
+          <t>evid_e3_anexo</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>${net_rel_27} = 'parceria' or ${net_rel_27} = 'articulacao'</t>
+          <t>Anexo (foto/documento) — opcional</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>net_atual_28</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Quilombolas</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>${net_rel_28} = 'parceria' or ${net_rel_28} = 'articulacao'</t>
+          <t>end_repeat</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>net_atual_29</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Agricultores familiares</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>${net_rel_29} = 'parceria' or ${net_rel_29} = 'articulacao'</t>
+          <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>net_atual_30</t>
+          <t>confirmacao</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Pescadores</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>${net_rel_30} = 'parceria' or ${net_rel_30} = 'articulacao'</t>
+          <t>Confirmação final</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>net_atual_31</t>
+          <t>confirmacao_msg</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>${net_rel_31} = 'parceria' or ${net_rel_31} = 'articulacao'</t>
+          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
+          <t>select_one confirmo</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>net_atual_32</t>
+          <t>confirmacao_envio</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Lideranças</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>${net_rel_32} = 'parceria' or ${net_rel_32} = 'articulacao'</t>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>net_atual_33</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Detentores de conhecimentos locais</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>${net_rel_33} = 'parceria' or ${net_rel_33} = 'articulacao'</t>
+          <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>net_atual_34</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Outro (comunidades e conhecimentos)</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>${net_rel_34} = 'parceria' or ${net_rel_34} = 'articulacao'</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>net_atual_outro</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Especifique (Outro) — contribuições atuais</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>selected(${net_atual_01}, 'outro') or selected(${net_atual_02}, 'outro') or selected(${net_atual_03}, 'outro') or selected(${net_atual_04}, 'outro') or selected(${net_atual_05}, 'outro') or selected(${net_atual_06}, 'outro') or selected(${net_atual_07}, 'outro') or selected(${net_atual_08}, 'outro') or selected(${net_atual_09}, 'outro') or selected(${net_atual_10}, 'outro') or selected(${net_atual_11}, 'outro') or selected(${net_atual_12}, 'outro') or selected(${net_atual_13}, 'outro') or selected(${net_atual_14}, 'outro') or selected(${net_atual_15}, 'outro') or selected(${net_atual_16}, 'outro') or selected(${net_atual_17}, 'outro') or selected(${net_atual_18}, 'outro') or selected(${net_atual_19}, 'outro') or selected(${net_atual_20}, 'outro') or selected(${net_atual_21}, 'outro') or selected(${net_atual_22}, 'outro') or selected(${net_atual_23}, 'outro') or selected(${net_atual_24}, 'outro') or selected(${net_atual_25}, 'outro') or selected(${net_atual_26}, 'outro') or selected(${net_atual_27}, 'outro') or selected(${net_atual_28}, 'outro') or selected(${net_atual_29}, 'outro') or selected(${net_atual_30}, 'outro') or selected(${net_atual_31}, 'outro') or selected(${net_atual_32}, 'outro') or selected(${net_atual_33}, 'outro') or selected(${net_atual_34}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>net_pot</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Q3.13. Contribuições potenciais — o que cada ator que existe no território poderia oferecer?</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>(${net_rel_01} != '' and ${net_rel_01} != 'nao_existe' and ${net_rel_01} != 'nao_sei') or (${net_rel_02} != '' and ${net_rel_02} != 'nao_existe' and ${net_rel_02} != 'nao_sei') or (${net_rel_03} != '' and ${net_rel_03} != 'nao_existe' and ${net_rel_03} != 'nao_sei') or (${net_rel_04} != '' and ${net_rel_04} != 'nao_existe' and ${net_rel_04} != 'nao_sei') or (${net_rel_05} != '' and ${net_rel_05} != 'nao_existe' and ${net_rel_05} != 'nao_sei') or (${net_rel_06} != '' and ${net_rel_06} != 'nao_existe' and ${net_rel_06} != 'nao_sei') or (${net_rel_07} != '' and ${net_rel_07} != 'nao_existe' and ${net_rel_07} != 'nao_sei') or (${net_rel_08} != '' and ${net_rel_08} != 'nao_existe' and ${net_rel_08} != 'nao_sei') or (${net_rel_09} != '' and ${net_rel_09} != 'nao_existe' and ${net_rel_09} != 'nao_sei') or (${net_rel_10} != '' and ${net_rel_10} != 'nao_existe' and ${net_rel_10} != 'nao_sei') or (${net_rel_11} != '' and ${net_rel_11} != 'nao_existe' and ${net_rel_11} != 'nao_sei') or (${net_rel_12} != '' and ${net_rel_12} != 'nao_existe' and ${net_rel_12} != 'nao_sei') or (${net_rel_13} != '' and ${net_rel_13} != 'nao_existe' and ${net_rel_13} != 'nao_sei') or (${net_rel_14} != '' and ${net_rel_14} != 'nao_existe' and ${net_rel_14} != 'nao_sei') or (${net_rel_15} != '' and ${net_rel_15} != 'nao_existe' and ${net_rel_15} != 'nao_sei') or (${net_rel_16} != '' and ${net_rel_16} != 'nao_existe' and ${net_rel_16} != 'nao_sei') or (${net_rel_17} != '' and ${net_rel_17} != 'nao_existe' and ${net_rel_17} != 'nao_sei') or (${net_rel_18} != '' and ${net_rel_18} != 'nao_existe' and ${net_rel_18} != 'nao_sei') or (${net_rel_19} != '' and ${net_rel_19} != 'nao_existe' and ${net_rel_19} != 'nao_sei') or (${net_rel_20} != '' and ${net_rel_20} != 'nao_existe' and ${net_rel_20} != 'nao_sei') or (${net_rel_21} != '' and ${net_rel_21} != 'nao_existe' and ${net_rel_21} != 'nao_sei') or (${net_rel_22} != '' and ${net_rel_22} != 'nao_existe' and ${net_rel_22} != 'nao_sei') or (${net_rel_23} != '' and ${net_rel_23} != 'nao_existe' and ${net_rel_23} != 'nao_sei') or (${net_rel_24} != '' and ${net_rel_24} != 'nao_existe' and ${net_rel_24} != 'nao_sei') or (${net_rel_25} != '' and ${net_rel_25} != 'nao_existe' and ${net_rel_25} != 'nao_sei') or (${net_rel_26} != '' and ${net_rel_26} != 'nao_existe' and ${net_rel_26} != 'nao_sei') or (${net_rel_27} != '' and ${net_rel_27} != 'nao_existe' and ${net_rel_27} != 'nao_sei') or (${net_rel_28} != '' and ${net_rel_28} != 'nao_existe' and ${net_rel_28} != 'nao_sei') or (${net_rel_29} != '' and ${net_rel_29} != 'nao_existe' and ${net_rel_29} != 'nao_sei') or (${net_rel_30} != '' and ${net_rel_30} != 'nao_existe' and ${net_rel_30} != 'nao_sei') or (${net_rel_31} != '' and ${net_rel_31} != 'nao_existe' and ${net_rel_31} != 'nao_sei') or (${net_rel_32} != '' and ${net_rel_32} != 'nao_existe' and ${net_rel_32} != 'nao_sei') or (${net_rel_33} != '' and ${net_rel_33} != 'nao_existe' and ${net_rel_33} != 'nao_sei') or (${net_rel_34} != '' and ${net_rel_34} != 'nao_existe' and ${net_rel_34} != 'nao_sei')</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>table-list</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>net_pot_01</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Secretaria de Educação</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>${net_rel_01} != '' and ${net_rel_01} != 'nao_existe' and ${net_rel_01} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>net_pot_02</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Secretaria de Meio Ambiente</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>${net_rel_02} != '' and ${net_rel_02} != 'nao_existe' and ${net_rel_02} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>net_pot_03</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Defesa Civil</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>${net_rel_03} != '' and ${net_rel_03} != 'nao_existe' and ${net_rel_03} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>net_pot_04</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Secretaria de Saúde</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>${net_rel_04} != '' and ${net_rel_04} != 'nao_existe' and ${net_rel_04} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>net_pot_05</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Assistência Social</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>${net_rel_05} != '' and ${net_rel_05} != 'nao_existe' and ${net_rel_05} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>net_pot_06</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Obras</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>${net_rel_06} != '' and ${net_rel_06} != 'nao_existe' and ${net_rel_06} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>net_pot_07</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Bombeiros</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>${net_rel_07} != '' and ${net_rel_07} != 'nao_existe' and ${net_rel_07} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>net_pot_08</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>UBS</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>${net_rel_08} != '' and ${net_rel_08} != 'nao_existe' and ${net_rel_08} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>net_pot_09</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Vigilância</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>${net_rel_09} != '' and ${net_rel_09} != 'nao_existe' and ${net_rel_09} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>net_pot_10</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Outro (poder público)</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>${net_rel_10} != '' and ${net_rel_10} != 'nao_existe' and ${net_rel_10} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>net_pot_11</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Universidade</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>${net_rel_11} != '' and ${net_rel_11} != 'nao_existe' and ${net_rel_11} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>net_pot_12</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Instituto Federal</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>${net_rel_12} != '' and ${net_rel_12} != 'nao_existe' and ${net_rel_12} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>net_pot_13</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Escola técnica</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>${net_rel_13} != '' and ${net_rel_13} != 'nao_existe' and ${net_rel_13} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>net_pot_14</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Centro de pesquisa</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>${net_rel_14} != '' and ${net_rel_14} != 'nao_existe' and ${net_rel_14} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>net_pot_15</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Museu</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>${net_rel_15} != '' and ${net_rel_15} != 'nao_existe' and ${net_rel_15} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>net_pot_16</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Jardim botânico</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>${net_rel_16} != '' and ${net_rel_16} != 'nao_existe' and ${net_rel_16} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>net_pot_17</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Outro (educação/ciência)</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>${net_rel_17} != '' and ${net_rel_17} != 'nao_existe' and ${net_rel_17} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>net_pot_18</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Associação de moradores</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>${net_rel_18} != '' and ${net_rel_18} != 'nao_existe' and ${net_rel_18} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>net_pot_19</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>ONG</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>${net_rel_19} != '' and ${net_rel_19} != 'nao_existe' and ${net_rel_19} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>net_pot_20</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Cooperativa</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>${net_rel_20} != '' and ${net_rel_20} != 'nao_existe' and ${net_rel_20} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>net_pot_21</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Catadores</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>${net_rel_21} != '' and ${net_rel_21} != 'nao_existe' and ${net_rel_21} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>net_pot_22</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Movimentos sociais</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>${net_rel_22} != '' and ${net_rel_22} != 'nao_existe' and ${net_rel_22} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>net_pot_23</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Coletivos</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>${net_rel_23} != '' and ${net_rel_23} != 'nao_existe' and ${net_rel_23} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>net_pot_24</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Grupos culturais</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>${net_rel_24} != '' and ${net_rel_24} != 'nao_existe' and ${net_rel_24} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>net_pot_25</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Organizações comunitárias/religiosas</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>${net_rel_25} != '' and ${net_rel_25} != 'nao_existe' and ${net_rel_25} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>net_pot_26</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Outro (sociedade civil)</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>${net_rel_26} != '' and ${net_rel_26} != 'nao_existe' and ${net_rel_26} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>net_pot_27</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Povos indígenas</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>${net_rel_27} != '' and ${net_rel_27} != 'nao_existe' and ${net_rel_27} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>net_pot_28</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Quilombolas</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>${net_rel_28} != '' and ${net_rel_28} != 'nao_existe' and ${net_rel_28} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>net_pot_29</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Agricultores familiares</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>${net_rel_29} != '' and ${net_rel_29} != 'nao_existe' and ${net_rel_29} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>net_pot_30</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Pescadores</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>${net_rel_30} != '' and ${net_rel_30} != 'nao_existe' and ${net_rel_30} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>net_pot_31</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Comunidades tradicionais</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>${net_rel_31} != '' and ${net_rel_31} != 'nao_existe' and ${net_rel_31} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>net_pot_32</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Lideranças</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>${net_rel_32} != '' and ${net_rel_32} != 'nao_existe' and ${net_rel_32} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>net_pot_33</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Detentores de conhecimentos locais</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>${net_rel_33} != '' and ${net_rel_33} != 'nao_existe' and ${net_rel_33} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>select_multiple contrib</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>net_pot_34</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Outro (comunidades e conhecimentos)</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>${net_rel_34} != '' and ${net_rel_34} != 'nao_existe' and ${net_rel_34} != 'nao_sei'</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>net_pot_outro</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Especifique (Outro) — contribuições potenciais</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>selected(${net_pot_01}, 'outro') or selected(${net_pot_02}, 'outro') or selected(${net_pot_03}, 'outro') or selected(${net_pot_04}, 'outro') or selected(${net_pot_05}, 'outro') or selected(${net_pot_06}, 'outro') or selected(${net_pot_07}, 'outro') or selected(${net_pot_08}, 'outro') or selected(${net_pot_09}, 'outro') or selected(${net_pot_10}, 'outro') or selected(${net_pot_11}, 'outro') or selected(${net_pot_12}, 'outro') or selected(${net_pot_13}, 'outro') or selected(${net_pot_14}, 'outro') or selected(${net_pot_15}, 'outro') or selected(${net_pot_16}, 'outro') or selected(${net_pot_17}, 'outro') or selected(${net_pot_18}, 'outro') or selected(${net_pot_19}, 'outro') or selected(${net_pot_20}, 'outro') or selected(${net_pot_21}, 'outro') or selected(${net_pot_22}, 'outro') or selected(${net_pot_23}, 'outro') or selected(${net_pot_24}, 'outro') or selected(${net_pot_25}, 'outro') or selected(${net_pot_26}, 'outro') or selected(${net_pot_27}, 'outro') or selected(${net_pot_28}, 'outro') or selected(${net_pot_29}, 'outro') or selected(${net_pot_30}, 'outro') or selected(${net_pot_31}, 'outro') or selected(${net_pot_32}, 'outro') or selected(${net_pot_33}, 'outro') or selected(${net_pot_34}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>select_multiple cat_ator</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>q3_14</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Q3.14. Quais atores são prioritários para fortalecer a relação? (NET_PRIORITY_ACTORS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>q3_15</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Q3.15. Cite o nome do ator mais relevante para a escola hoje (ex.: UBS Vila Nova)</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>select_one sim_nao_ns</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>q3_16</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Q3.16. A escola sabe a quem contatar em uma emergência climática?</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>q3_17</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Q3.17. Quais são esses contatos?</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>${q3_16}='sim'</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>select_one sim_nao_ns</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>q3_18</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Q3.18. Existe um procedimento de emergência definido para eventos climáticos?</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>select_one sim_nao_ns</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>q3_19</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Q3.19. Esse procedimento está documentado/formalizado?</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>${q3_18}='sim'</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>q3_20</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Q3.20. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>select_multiple canais</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>q3_21</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Q3.21. Canais de comunicação da escola com a comunidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>q3_21_outro</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>selected(${q3_21}, 'outro')</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>select_one suficiente</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>q3_22</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Q3.22. Esses canais seriam suficientes numa emergência?</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>q3_23</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Q3.23. Algum grupo fica de fora desses canais de comunicação?</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>q3_24</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Q3.24. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>q3_25</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Q3.25. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>select_multiple barr_artic</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>q3_26</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Q3.26. Barreiras para articular com atores do território</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>q3_26_outro</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>selected(${q3_26}, 'outro')</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>q3_27</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Q3.27. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>q3_28</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Q3.28. Quem participou desse caso?</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>${q3_27} != ''</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>q3_29</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Q3.29. O que funcionou bem?</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>${q3_27} != ''</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>q3_30</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Q3.30. Quais foram as dificuldades?</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>${q3_27} != ''</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>q3_31</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Q3.31. O que essa experiência ensinou?</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>${q3_27} != ''</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>q3_32</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Q3.32. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>q3_33</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Q3.33. Por quê?</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>${q3_32} != ''</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>begin_repeat</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>evid_e3</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Evidências — Evidências sobre participação e redes</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>evid_e3_nota</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>select_one tipo_evid</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>evid_e3_tipo</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Tipo de evidência</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>evid_e3_tipo_outro</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>${evid_e3_tipo}='outro'</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>evid_e3_desc</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Descreva a evidência</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>evid_e3_anexo</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Anexo (foto/documento) — opcional</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>confirmacao</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Confirmação final</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>confirmacao_msg</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>select_one confirmo</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>confirmacao_envio</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Revisei minhas respostas e confirmo o envio.</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
@@ -5987,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C266"/>
+  <dimension ref="A1:C259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10039,474 +8421,355 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>apoio_tecnico</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Apoio técnico</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>conhecimentos_tradicionais_locai</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Conhecimentos tradicionais/locais</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>contrib</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
-        <is>
-          <t>Falta de tempo</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>barr_artic</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>outro</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Outra</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>nivel_rel_grade</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>nao_existe</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Não existe no território</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>nivel_rel_grade</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>nao_sei</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Não sei se existe</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>nivel_rel_grade</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>sem_contato</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Existe, mas nunca houve contato</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>nivel_rel_grade</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>contato_pontual</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>nivel_rel_grade</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>parceria</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>nivel_rel_grade</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>articulacao</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
         <is>
           <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>

--- a/kobo/professores_semana2_diagnostico.xlsx
+++ b/kobo/professores_semana2_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Q2.7. Como ocorre a articulação entre áreas/disciplinas?</t>
+          <t>Q2.7. Como ocorre a articulação da educação ambiental entre áreas/disciplinas?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Q2.18. Que problema territorial foi abordado?</t>
+          <t>Q2.18. Qual problema territorial foi abordado?</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Q2.20. O que essa atividade mudou ou gerou?</t>
+          <t>Q2.20. Quais foram os resultados dessa atividade (ex. O que essa atividade mudou ou gerou?)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Q2.26. Frequência de uso do território como espaço pedagógico</t>
+          <t>Q2.26. Frequência de uso pedagógico dos espaços do entorno da escola, como aulas de campo, visitas e trilhas e outras atividades educativas fora da sala de aula.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -1810,39 +1810,44 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>q2_28</t>
+          <t>q2_27_quais</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Q2.28. Houve formação recente em Educação Ambiental?</t>
+          <t>Quais problemas locais/territoriais são abordados?</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>${q2_27}='sim'</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>q2_29</t>
+          <t>q2_28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Q2.29. Quem ofereceu a formação?</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>${q2_28}='sim'</t>
+          <t>Q2.28. Houve formação recente em Educação Ambiental?</t>
         </is>
       </c>
     </row>
@@ -1854,176 +1859,181 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>q2_30</t>
+          <t>q2_29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Q2.30. Quais temas foram abordados?</t>
+          <t>Q2.29. Quem ofereceu a formação?</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>${q2_28}='sim'</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>select_one impacto_form</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q2_31</t>
+          <t>q2_30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Q2.31. Qual o impacto dessa formação na prática?</t>
+          <t>Q2.30. Quais temas foram abordados?</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>${q2_28}='sim'</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one impacto_form</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>q2_32</t>
+          <t>q2_31</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Q2.32. Dê um exemplo desse impacto</t>
+          <t>Q2.31. Qual o impacto dessa formação na prática?</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>${q2_28}='sim'</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>select_one confianca</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>q2_33</t>
+          <t>q2_32</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Q2.33. Quão confiante você se sente para trabalhar Educação Ambiental hoje?</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Escala de 1 (nada confiante) a 5 (muito confiante).</t>
+          <t>Q2.32. Dê um exemplo desse impacto</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>${q2_28}='sim'</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>horizontal-compact</t>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>select_multiple apoio</t>
+          <t>select_one confianca</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>q2_34</t>
+          <t>q2_33</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Q2.34. Que tipo de apoio faria diferença?</t>
+          <t>Q2.33. Quão confiante você se sente para trabalhar Educação Ambiental hoje?</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Escala de 1 (nada confiante) a 5 (muito confiante).</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>horizontal-compact</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple apoio</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>q2_34_outro</t>
+          <t>q2_34</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>selected(${q2_34}, 'outro')</t>
+          <t>Q2.34. Que tipo de apoio faria diferença para integração da Educação Ambiental no território escolar?</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>t2_35</t>
+          <t>q2_34_outro</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Q2.35. Intensidade de cada barreira percebida</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>table-list</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>selected(${q2_34}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>select_one intensidade</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>q2_35_01</t>
+          <t>t2_35</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Q2.35. Intensidade de cada barreira percebida</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>table-list</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2045,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>q2_35_02</t>
+          <t>q2_35_01</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2062,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>q2_35_03</t>
+          <t>q2_35_02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2079,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>q2_35_04</t>
+          <t>q2_35_03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2096,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>q2_35_05</t>
+          <t>q2_35_04</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2113,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>q2_35_06</t>
+          <t>q2_35_05</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -2120,12 +2130,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>q2_35_07</t>
+          <t>q2_35_06</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -2137,12 +2147,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>q2_35_08</t>
+          <t>q2_35_07</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2164,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>q2_35_09</t>
+          <t>q2_35_08</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2181,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>q2_35_10</t>
+          <t>q2_35_09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2198,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>q2_35_11</t>
+          <t>q2_35_10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
@@ -2205,706 +2215,721 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>q2_35_12</t>
+          <t>q2_35_11</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one intensidade</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>q2_35_12</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Outras</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>q2_35a</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Q2.35a. Você marcou uma intensidade para "Outras" barreiras acima — quais são elas?</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>${q2_35_12} != ''</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>select_one barreiras</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>q2_36</t>
+          <t>q2_35a</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Q2.36. Principal barreira hoje</t>
+          <t>Q2.35a. Você marcou uma intensidade para "Outras" barreiras acima — quais são elas?</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>${q2_35_12} != ''</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one barreiras</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>q2_36_outro</t>
+          <t>q2_36</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>${q2_36}='outro'</t>
+          <t>Q2.36. Principal barreira hoje</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>select_multiple materiais</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>q2_37</t>
+          <t>q2_36_outro</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Q2.37. Materiais didáticos utilizados</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>${q2_36}='outro'</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple materiais</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>q2_37_outro</t>
+          <t>q2_37</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>selected(${q2_37}, 'outro')</t>
+          <t>Q2.37. Materiais didáticos utilizados (para Educação Ambiental e/ou no dia a dia escolar)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Indique todos os que se aplicam, tanto os usados especificamente em Educação Ambiental quanto os do dia a dia escolar.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>select_one acesso_mat</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>q2_38</t>
+          <t>q2_37_outro</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Q2.38. Facilidade de acesso a esses materiais</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>selected(${q2_37}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one acesso_mat</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>q2_39</t>
+          <t>q2_38</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Q2.39. Que materiais fazem falta?</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Q2.38. Facilidade de acesso a esses materiais</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>select_one part_estud</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>q2_40</t>
+          <t>q2_39</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Q2.40. Como caracterizar, de modo geral, a participação dos estudantes nas ações de EA?</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>Q2.39. Quais materiais fazem falta?</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>select_one continuidade_proj</t>
+          <t>select_one part_estud</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>q2_41</t>
+          <t>q2_40</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Q2.41. De modo geral, a continuidade dos projetos de EA está...</t>
+          <t>Q2.40. Como caracterizar, de modo geral, a participação dos estudantes nas ações de EA?</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one continuidade_proj</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>e2_leitura</t>
+          <t>q2_41</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Como o sistema está lendo suas respostas (revise e confirme) — no Kobo não há leitura automática: a tutoria/quem aplica o formulário deve revisar as respostas desta etapa antes de responder abaixo.</t>
+          <t>Q2.41. De modo geral, a continuidade dos projetos de EA está...</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>q2_42</t>
+          <t>evid_e2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Q2.42. Essa leitura reflete a realidade da escola?</t>
+          <t>Evidências — Evidências sobre Educação Ambiental</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>q2_43</t>
+          <t>evid_e2_nota</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Q2.43. O que precisa ser corrigido ou complementado?</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>${q2_42}='nao' or ${q2_42}='nao_sabemos'</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one tipo_evid</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>evid_e2</t>
+          <t>evid_e2_tipo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Evidências — Evidências sobre Educação Ambiental</t>
+          <t>Tipo de evidência</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>evid_e2_nota</t>
+          <t>evid_e2_tipo_outro</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>${evid_e2_tipo}='outro'</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>select_one tipo_evid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>evid_e2_tipo</t>
+          <t>evid_e2_desc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tipo de evidência</t>
+          <t>Descreva a evidência</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>evid_e2_tipo_outro</t>
+          <t>evid_e2_anexo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>${evid_e2_tipo}='outro'</t>
+          <t>Anexo (foto/documento) — opcional</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>evid_e2_desc</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Descreva a evidência</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>end_repeat</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>evid_e2_anexo</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Anexo (foto/documento) — opcional</t>
+          <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>etapa3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Etapa 3 — Participação e Redes</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_multiple quem_part</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>q3_1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Q3.1. Quem participa das ações de Educação Ambiental hoje?</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>etapa3</t>
+          <t>q3_1_outro</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Etapa 3 — Participação e Redes</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>selected(${q3_1}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>select_multiple quem_part</t>
+          <t>select_one nivel_part</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>q3_1</t>
+          <t>q3_2</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Q3.1. Quem participa das ações de Educação Ambiental hoje?</t>
+          <t>Q3.2. Como essa participação costuma acontecer?</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Participação não é sinônimo de presença — o que importa é o nível de envolvimento na decisão.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple esp_estud</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>q3_1_outro</t>
+          <t>q3_3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>selected(${q3_1}, 'outro')</t>
+          <t>Q3.3. Espaços de participação estudantil existentes</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>"Nenhum" não pode ser combinado com outras opções.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>select_one nivel_part</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>q3_2</t>
+          <t>q3_3_outro</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Q3.2. Como essa participação costuma acontecer?</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Participação não é sinônimo de presença — o que importa é o nível de envolvimento na decisão.</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>selected(${q3_3}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>select_multiple esp_estud</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>q3_3</t>
+          <t>q3_4</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Q3.3. Espaços de participação estudantil existentes</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>not(selected(., 'nenhum') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>"Nenhum" não pode ser combinado com outras opções.</t>
+          <t>Q3.4. Descreva práticas concretas de participação estudantil (se houver)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one env_fam</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>q3_3_outro</t>
+          <t>q3_5</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>selected(${q3_3}, 'outro')</t>
+          <t>Q3.5. Nível de envolvimento das famílias com a escola</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple barr_fam</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>q3_4</t>
+          <t>q3_6</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Q3.4. Descreva práticas concretas de participação estudantil (se houver)</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Q3.6. Barreiras à participação das famílias</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>q3_5</t>
+          <t>q3_6_outro</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Q3.5. O nível de participação estudantil descrito na Etapa 2 continua condizente?</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>selected(${q3_6}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>select_one env_fam</t>
+          <t>select_one freq5</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>q3_6</t>
+          <t>q3_7</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Q3.6. Nível de envolvimento das famílias com a escola</t>
+          <t>Q3.7. Frequência de atividades da escola com o território/comunidade</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>select_multiple barr_fam</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>q3_7</t>
+          <t>q3_8</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Q3.7. Barreiras à participação das famílias</t>
+          <t>Q3.8. Quais atividades com o território/comunidade já ocorreram?</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>q3_7_outro</t>
+          <t>q3_9</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>selected(${q3_7}, 'outro')</t>
+          <t>Q3.9. A escola tem mecanismos de escuta da comunidade?</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>select_one freq5</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>q3_8</t>
+          <t>q3_10_quais</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Q3.8. Frequência de atividades da escola com o território/comunidade</t>
+          <t>Quais mecanismos de escuta existem?</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>${q3_9}='sim'</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>q3_9</t>
+          <t>net_nota</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Q3.9. Quais atividades com o território/comunidade já ocorreram?</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Atores do território (NET_ACTORS). Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se a escola já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>q3_10</t>
+          <t>net_rel</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Q3.10. A escola tem mecanismos de escuta da comunidade?</t>
+          <t>Q3.10. Para cada tipo de ator, qual é a relação atual da escola com ele?</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>table-list</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>net_nota</t>
+          <t>net_rel_01</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Atores do território (NET_ACTORS). Existência, contato, parceria e articulação permanente são níveis diferentes — não confunda um com o outro. Só marque "Parceria" ou "Articulação permanente" se a escola já colabora de fato com esse ator; se ele apenas existe no território ou já houve um contato pontual, isso ainda NÃO é parceria.</t>
+          <t>Secretaria de Educação</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one nivel_rel_grade</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>net_rel</t>
+          <t>net_rel_02</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Q3.11. Para cada tipo de ator, qual é a relação atual da escola com ele?</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>table-list</t>
+          <t>Secretaria de Meio Ambiente</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2941,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>net_rel_01</t>
+          <t>net_rel_03</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -2938,12 +2963,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>net_rel_02</t>
+          <t>net_rel_04</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -2960,12 +2985,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>net_rel_03</t>
+          <t>net_rel_05</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Assistência Social</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -2982,12 +3007,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>net_rel_04</t>
+          <t>net_rel_06</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Obras</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3004,12 +3029,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>net_rel_05</t>
+          <t>net_rel_07</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Bombeiros</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3026,12 +3051,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>net_rel_06</t>
+          <t>net_rel_08</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -3048,12 +3073,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>net_rel_07</t>
+          <t>net_rel_09</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Vigilância</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -3070,12 +3095,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>net_rel_08</t>
+          <t>net_rel_10</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -3092,12 +3117,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>net_rel_09</t>
+          <t>net_rel_11</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Universidade</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -3114,12 +3139,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>net_rel_10</t>
+          <t>net_rel_12</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -3136,12 +3161,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>net_rel_11</t>
+          <t>net_rel_13</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Escola técnica</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -3158,12 +3183,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>net_rel_12</t>
+          <t>net_rel_14</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -3180,12 +3205,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>net_rel_13</t>
+          <t>net_rel_15</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>Museu</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -3202,12 +3227,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>net_rel_14</t>
+          <t>net_rel_16</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -3224,12 +3249,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>net_rel_15</t>
+          <t>net_rel_17</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -3246,12 +3271,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>net_rel_16</t>
+          <t>net_rel_18</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -3268,12 +3293,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>net_rel_17</t>
+          <t>net_rel_19</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>ONG</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -3290,12 +3315,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>net_rel_18</t>
+          <t>net_rel_20</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -3312,12 +3337,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>net_rel_19</t>
+          <t>net_rel_21</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Catadores</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -3334,12 +3359,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>net_rel_20</t>
+          <t>net_rel_22</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -3356,12 +3381,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>net_rel_21</t>
+          <t>net_rel_23</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Coletivos</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -3378,12 +3403,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>net_rel_22</t>
+          <t>net_rel_24</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -3400,12 +3425,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>net_rel_23</t>
+          <t>net_rel_25</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -3422,12 +3447,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>net_rel_24</t>
+          <t>net_rel_26</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -3444,12 +3469,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>net_rel_25</t>
+          <t>net_rel_27</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -3466,12 +3491,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>net_rel_26</t>
+          <t>net_rel_28</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Quilombolas</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -3488,12 +3513,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>net_rel_27</t>
+          <t>net_rel_29</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -3510,12 +3535,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>net_rel_28</t>
+          <t>net_rel_30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Pescadores</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -3532,12 +3557,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>net_rel_29</t>
+          <t>net_rel_31</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -3554,12 +3579,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>net_rel_30</t>
+          <t>net_rel_32</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Lideranças</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -3576,12 +3601,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>net_rel_31</t>
+          <t>net_rel_33</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -3598,12 +3623,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>net_rel_32</t>
+          <t>net_rel_34</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -3615,68 +3640,68 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>select_one nivel_rel_grade</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>net_rel_33</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Detentores de conhecimentos locais</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>select_one nivel_rel_grade</t>
+          <t>select_multiple cat_ator</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>net_rel_34</t>
+          <t>q3_11</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>Q3.11. Quais atores são prioritários para fortalecer a relação da escola com o território? (NET_PRIORITY_ACTORS)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>q3_12</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Q3.12. Cite o nome do ator mais relevante para a escola hoje (ex.: UBS Vila Nova)</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>select_multiple cat_ator</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>q3_12</t>
+          <t>q3_13</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Q3.12. Quais atores são prioritários para fortalecer a relação? (NET_PRIORITY_ACTORS)</t>
+          <t>Q3.13. A escola sabe a quem contatar em uma emergência climática?</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3713,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>q3_13</t>
+          <t>q3_14</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Q3.13. Cite o nome do ator mais relevante para a escola hoje (ex.: UBS Vila Nova)</t>
+          <t>Q3.14. Quais são esses contatos?</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>${q3_13}='sim'</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -3710,12 +3740,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>q3_14</t>
+          <t>q3_15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Q3.14. A escola sabe a quem contatar em uma emergência climática?</t>
+          <t>Q3.15. Existe um procedimento de emergência definido para eventos climáticos?</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -3727,71 +3757,61 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>q3_15</t>
+          <t>q3_16</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Q3.15. Quais são esses contatos?</t>
+          <t>Q3.16. Esse procedimento está documentado/formalizado?</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>${q3_14}='sim'</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>${q3_15}='sim'</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>q3_16</t>
+          <t>q3_17</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Q3.16. Existe um procedimento de emergência definido para eventos climáticos?</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>Q3.17. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>select_multiple canais</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>q3_17</t>
+          <t>q3_18</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Q3.17. Esse procedimento está documentado/formalizado?</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>${q3_16}='sim'</t>
+          <t>Q3.18. Canais de comunicação da escola com a comunidade</t>
         </is>
       </c>
     </row>
@@ -3803,24 +3823,24 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>q3_18</t>
+          <t>q3_18_outro</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Q3.18. Que ações de preparação já foram feitas (simulados, sinalização, etc.)?</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>selected(${q3_18}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>select_multiple canais</t>
+          <t>select_one suficiente</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3830,7 +3850,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Q3.19. Canais de comunicação da escola com a comunidade</t>
+          <t>Q3.19. Esses canais seriam suficientes numa emergência?</t>
         </is>
       </c>
     </row>
@@ -3842,34 +3862,44 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>q3_19_outro</t>
+          <t>q3_20</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>selected(${q3_19}, 'outro')</t>
+          <t>Q3.20. Algum grupo fica de fora desses canais de comunicação?</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>select_one suficiente</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>q3_20</t>
+          <t>q3_21</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Q3.20. Esses canais seriam suficientes numa emergência?</t>
+          <t>Q3.21. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
@@ -3881,12 +3911,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>q3_21</t>
+          <t>q3_22</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Q3.21. Algum grupo fica de fora desses canais de comunicação?</t>
+          <t>Q3.22. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -3898,27 +3928,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple barr_artic</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>q3_22</t>
+          <t>q3_23</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Q3.22. Que capacidades/conhecimentos a comunidade já possui e podem ser mobilizados?</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Ex.: conhecimento tradicional sobre o clima local, organização comunitária, mutirões, saberes de manejo.</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Q3.23. Barreiras para articular com atores do território</t>
         </is>
       </c>
     </row>
@@ -3930,24 +3950,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>q3_23</t>
+          <t>q3_23_outro</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Q3.23. Quais dessas capacidades parecem mais estratégicas de fortalecer?</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>selected(${q3_23}, 'outro')</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>select_multiple barr_artic</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3957,7 +3977,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Q3.24. Barreiras para articular com atores do território</t>
+          <t>Q3.24. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
@@ -3969,17 +3994,22 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>q3_24_outro</t>
+          <t>q3_25</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Q3.25. Quem participou desse caso?</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>selected(${q3_24}, 'outro')</t>
+          <t>${q3_24} != ''</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
@@ -3991,12 +4021,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>q3_25</t>
+          <t>q3_26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Q3.25. Descreva um caso concreto de articulação (bem ou malsucedida) com a comunidade/rede</t>
+          <t>Q3.26. O que funcionou bem?</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>${q3_24} != ''</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -4013,17 +4048,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>q3_26</t>
+          <t>q3_27</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Q3.26. Quem participou desse caso?</t>
+          <t>Q3.27. Quais foram as dificuldades?</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>${q3_25} != ''</t>
+          <t>${q3_24} != ''</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -4040,17 +4075,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>q3_27</t>
+          <t>q3_28</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Q3.27. O que funcionou bem?</t>
+          <t>Q3.28. O que essa experiência ensinou?</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>${q3_25} != ''</t>
+          <t>${q3_24} != ''</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -4067,17 +4102,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>q3_28</t>
+          <t>q3_29</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Q3.28. Quais foram as dificuldades?</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>${q3_25} != ''</t>
+          <t>Q3.29. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -4094,17 +4124,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>q3_29</t>
+          <t>q3_30</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Q3.29. O que essa experiência ensinou?</t>
+          <t>Q3.30. Por quê?</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>${q3_25} != ''</t>
+          <t>${q3_29} != ''</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -4116,243 +4146,194 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>q3_30</t>
+          <t>evid_e3</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Q3.30. Se houvesse uma relação prioritária para fortalecer agora, qual seria?</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Evidências — Evidências sobre participação e redes</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>q3_31</t>
+          <t>evid_e3_nota</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Q3.31. Por quê?</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>${q3_30} != ''</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one tipo_evid</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>evid_e3</t>
+          <t>evid_e3_tipo</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Evidências — Evidências sobre participação e redes</t>
+          <t>Tipo de evidência</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>evid_e3_nota</t>
+          <t>evid_e3_tipo_outro</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Evidências sustentam análises futuras (problemas, prioridades, plano de ação). Registrar não é obrigatório para todo campo, mas fortalece a rastreabilidade do diagnóstico.</t>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>${evid_e3_tipo}='outro'</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>select_one tipo_evid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>evid_e3_tipo</t>
+          <t>evid_e3_desc</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tipo de evidência</t>
+          <t>Descreva a evidência</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>evid_e3_tipo_outro</t>
+          <t>evid_e3_anexo</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>${evid_e3_tipo}='outro'</t>
+          <t>Anexo (foto/documento) — opcional</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>evid_e3_desc</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Descreva a evidência</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>end_repeat</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>evid_e3_anexo</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Anexo (foto/documento) — opcional</t>
+          <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>confirmacao</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Confirmação final</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>confirmacao_msg</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one confirmo</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>confirmacao</t>
+          <t>confirmacao_envio</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Confirmação final</t>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>confirmacao_msg</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Semana 2/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
+          <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
-        <is>
-          <t>select_one confirmo</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>confirmacao_envio</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Revisei minhas respostas e confirmo o envio.</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
@@ -4369,7 +4350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C259"/>
+  <dimension ref="A1:C261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6619,17 +6600,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6622,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>material_didatico</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Material didático</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6639,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>tempo_de_planejamento</t>
+          <t>material_didatico</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tempo de planejamento</t>
+          <t>Material didático</t>
         </is>
       </c>
     </row>
@@ -6675,12 +6656,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>tempo_de_planejamento</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Tempo de planejamento</t>
         </is>
       </c>
     </row>
@@ -6692,12 +6673,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -6709,12 +6690,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
@@ -6726,29 +6707,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6741,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>curriculo_sobrecarregado</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6758,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>curriculo_sobrecarregado</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6775,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -6811,12 +6792,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -6828,12 +6809,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -6845,12 +6826,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>planejamento_coletivo</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -6862,12 +6843,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>interdisciplinaridade</t>
+          <t>planejamento_coletivo</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -6879,12 +6860,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>informacoes_territoriais</t>
+          <t>interdisciplinaridade</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6877,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>descontinuidade</t>
+          <t>informacoes_territoriais</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6894,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>rotatividade_de_profissionais</t>
+          <t>descontinuidade</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
@@ -6930,29 +6911,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>rotatividade_de_profissionais</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
@@ -6964,12 +6945,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6962,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -6998,29 +6979,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>livros_didaticos</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Livros didáticos</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7013,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>livros_didaticos</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Livros didáticos</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7030,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7047,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>kits_cientificos</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Kits científicos</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
@@ -7083,12 +7064,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_escola</t>
+          <t>kits_cientificos</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Materiais produzidos pela escola</t>
+          <t>Kits científicos</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7081,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>materiais_produzidos_pela_escola</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Materiais produzidos pela escola</t>
         </is>
       </c>
     </row>
@@ -7117,29 +7098,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7151,12 +7132,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
@@ -7168,12 +7149,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
@@ -7185,12 +7166,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
@@ -7202,29 +7183,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7236,12 +7217,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
@@ -7253,12 +7234,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
@@ -7270,12 +7251,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
@@ -7287,29 +7268,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7321,12 +7302,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7319,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
@@ -7355,29 +7336,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7389,12 +7370,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -7406,12 +7387,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7404,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7421,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7438,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -7474,46 +7455,46 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>instituicao_parceira</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Instituição parceira</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -7525,12 +7506,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7523,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
@@ -7559,46 +7540,46 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>assembleias</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Assembleias</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7610,12 +7591,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>projetos_protagonizados_por_estu</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Projetos protagonizados por estudantes</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -7627,12 +7608,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>conselhos</t>
+          <t>assembleias</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Conselhos</t>
+          <t>Assembleias</t>
         </is>
       </c>
     </row>
@@ -7644,12 +7625,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>projetos_protagonizados_por_estu</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Projetos protagonizados por estudantes</t>
         </is>
       </c>
     </row>
@@ -7661,46 +7642,46 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conselhos</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Conselhos</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -7712,12 +7693,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
@@ -7729,12 +7710,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
@@ -7746,46 +7727,46 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7797,12 +7778,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7795,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
@@ -7831,46 +7812,46 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -7882,12 +7863,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7880,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -7916,12 +7897,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -7933,12 +7914,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -7950,12 +7931,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -7967,12 +7948,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -7984,12 +7965,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -8001,12 +7982,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -8018,12 +7999,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8016,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -8052,12 +8033,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8050,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8067,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -8103,12 +8084,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8101,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8118,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8135,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -8171,12 +8152,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -8188,12 +8169,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8186,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -8222,12 +8203,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8220,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -8256,12 +8237,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8254,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -8290,12 +8271,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -8307,12 +8288,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8305,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -8341,12 +8322,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8339,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
@@ -8375,12 +8356,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
@@ -8392,12 +8373,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
@@ -8409,46 +8390,46 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -8460,12 +8441,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8458,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
@@ -8494,12 +8475,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
@@ -8511,46 +8492,46 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8543,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -8579,46 +8560,46 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8611,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
@@ -8647,12 +8628,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
@@ -8664,46 +8645,46 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Não existe no território</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Não sei se existe</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -8715,12 +8696,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>sem_contato</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Existe, mas nunca houve contato</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
@@ -8732,12 +8713,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8730,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
@@ -8766,10 +8747,44 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
+          <t>contato_pontual</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>parceria</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Parceria — já colaboram em ações combinadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
           <t>articulacao</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>

--- a/kobo/professores_semana2_diagnostico.xlsx
+++ b/kobo/professores_semana2_diagnostico.xlsx
@@ -901,6 +901,16 @@
           <t>Q2.6. Áreas curriculares que já trabalharam Educação Ambiental</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -979,6 +989,16 @@
           <t>Q2.9. Em que contextos essas práticas costumam acontecer?</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1613,6 +1633,16 @@
           <t>Q2.22. Quais temas são mais difíceis de trabalhar?</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1701,6 +1731,16 @@
           <t>Marque todos os que já foram usados, mesmo que raramente.</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2333,6 +2373,16 @@
       <c r="D96" t="inlineStr">
         <is>
           <t>Indique todos os que se aplicam, tanto os usados especificamente em Educação Ambiental quanto os do dia a dia escolar.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C261"/>
+  <dimension ref="A1:C266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5223,17 +5273,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>disciplinas_separadas</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Disciplinas separadas</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5245,12 +5295,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>mesmo_tema_sem_planejamento_conj</t>
+          <t>disciplinas_separadas</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mesmo tema, sem planejamento conjunto</t>
+          <t>Disciplinas separadas</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5312,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>algum_planejamento_conjunto</t>
+          <t>mesmo_tema_sem_planejamento_conj</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algum planejamento conjunto</t>
+          <t>Mesmo tema, sem planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5329,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>investigacao_conjunta</t>
+          <t>algum_planejamento_conjunto</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Investigação conjunta</t>
+          <t>Algum planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5346,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>objetivos_comuns</t>
+          <t>investigacao_conjunta</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Objetivos comuns</t>
+          <t>Investigação conjunta</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5363,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>intervencao_territorial_coletiva</t>
+          <t>objetivos_comuns</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Intervenção territorial coletiva</t>
+          <t>Objetivos comuns</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5380,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sem_articulacao</t>
+          <t>intervencao_territorial_coletiva</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sem articulação</t>
+          <t>Intervenção territorial coletiva</t>
         </is>
       </c>
     </row>
@@ -5347,29 +5397,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>sem_articulacao</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Sem articulação</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Diária</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5431,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>Diária</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5448,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>semanal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Semanal</t>
         </is>
       </c>
     </row>
@@ -5415,12 +5465,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>esporadica</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Esporádica</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -5432,12 +5482,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>esporadica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Esporádica</t>
         </is>
       </c>
     </row>
@@ -5449,12 +5499,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nao_ocorre</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Não ocorre</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
@@ -5466,29 +5516,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao_ocorre</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não ocorre</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sala_de_aula</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sala de aula</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5550,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>patio_area_externa</t>
+          <t>sala_de_aula</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pátio/área externa</t>
+          <t>Sala de aula</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5567,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>visita_de_campo</t>
+          <t>patio_area_externa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Visita de campo</t>
+          <t>Pátio/área externa</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5584,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>projeto_especial</t>
+          <t>visita_de_campo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Projeto especial</t>
+          <t>Visita de campo</t>
         </is>
       </c>
     </row>
@@ -5551,12 +5601,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>feira</t>
+          <t>projeto_especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Feira</t>
+          <t>Projeto especial</t>
         </is>
       </c>
     </row>
@@ -5568,46 +5618,46 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>feira</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Feira</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>professor_individualmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Professor(a) individualmente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>grupo_de_professores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Grupo de professores(as)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5669,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>coordenacao_pedagogica</t>
+          <t>professor_individualmente</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Coordenação pedagógica</t>
+          <t>Professor(a) individualmente</t>
         </is>
       </c>
     </row>
@@ -5636,12 +5686,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>grupo_de_professores</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Grupo de professores(as)</t>
         </is>
       </c>
     </row>
@@ -5653,12 +5703,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>coordenacao_pedagogica</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Coordenação pedagógica</t>
         </is>
       </c>
     </row>
@@ -5670,46 +5720,46 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>participante_pontual</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Participante pontual</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -5721,12 +5771,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5788,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>participante_pontual</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Participante pontual</t>
         </is>
       </c>
     </row>
@@ -5755,46 +5805,46 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>depende_da_permanencia_de_profes</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Depende da permanência de professor(a) específico(a)</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tem continuidade institucional garantida</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5806,12 +5856,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>depende_da_permanencia_de_profes</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Depende da permanência de professor(a) específico(a)</t>
         </is>
       </c>
     </row>
@@ -5823,46 +5873,46 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Tem continuidade institucional garantida</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nunca</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5874,12 +5924,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>nunca</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Nunca</t>
         </is>
       </c>
     </row>
@@ -5891,12 +5941,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>frequentemente</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Frequentemente</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
@@ -5908,46 +5958,46 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>frequentemente</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Frequentemente</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>biodiversidade</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Biodiversidade</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -5959,12 +6009,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>residuos</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Resíduos</t>
+          <t>Água</t>
         </is>
       </c>
     </row>
@@ -5976,12 +6026,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>mudancas_climaticas</t>
+          <t>biodiversidade</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mudanças climáticas</t>
+          <t>Biodiversidade</t>
         </is>
       </c>
     </row>
@@ -5993,12 +6043,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>residuos</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Resíduos</t>
         </is>
       </c>
     </row>
@@ -6010,12 +6060,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>alimentacao</t>
+          <t>mudancas_climaticas</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Mudanças climáticas</t>
         </is>
       </c>
     </row>
@@ -6027,12 +6077,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>consumo</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Energia</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6094,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>saneamento</t>
+          <t>alimentacao</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Alimentação</t>
         </is>
       </c>
     </row>
@@ -6061,12 +6111,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>consumo</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Consumo</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6128,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>riscos_desastres</t>
+          <t>saneamento</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Riscos/desastres</t>
+          <t>Saneamento</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6145,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>justica_socioambiental</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Justiça socioambiental</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6162,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>riscos_desastres</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Riscos/desastres</t>
         </is>
       </c>
     </row>
@@ -6129,12 +6179,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>conflitos</t>
+          <t>justica_socioambiental</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Conflitos</t>
+          <t>Justiça socioambiental</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6196,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -6163,63 +6213,63 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conflitos</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Conflitos</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>falta_de_formacao</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Falta de formação</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>falta_de_material</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Falta de material</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>tema_sensivel_delicado</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tema sensível/delicado</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6231,12 +6281,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>falta_de_formacao</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Falta de formação</t>
         </is>
       </c>
     </row>
@@ -6248,12 +6298,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>curriculo</t>
+          <t>falta_de_material</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Currículo</t>
+          <t>Falta de material</t>
         </is>
       </c>
     </row>
@@ -6265,63 +6315,63 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>tema_sensivel_delicado</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Tema sensível/delicado</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>aula_expositiva</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Aula expositiva</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>projeto</t>
+          <t>curriculo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Currículo</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>oficina</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6333,12 +6383,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>saida_de_campo</t>
+          <t>aula_expositiva</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Saída de campo</t>
+          <t>Aula expositiva</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6400,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>horta_experimentacao</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Horta/experimentação</t>
+          <t>Projeto</t>
         </is>
       </c>
     </row>
@@ -6367,12 +6417,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>rodas_de_conversa</t>
+          <t>oficina</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rodas de conversa</t>
+          <t>Oficina</t>
         </is>
       </c>
     </row>
@@ -6384,12 +6434,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>producao_audiovisual</t>
+          <t>saida_de_campo</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Produção audiovisual</t>
+          <t>Saída de campo</t>
         </is>
       </c>
     </row>
@@ -6401,12 +6451,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cartografia</t>
+          <t>horta_experimentacao</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cartografia</t>
+          <t>Horta/experimentação</t>
         </is>
       </c>
     </row>
@@ -6418,80 +6468,80 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>rodas_de_conversa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Rodas de conversa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>producao_audiovisual</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Produção audiovisual</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>cartografia</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>Cartografia</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>significativo</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Significativo</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6503,80 +6553,80 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1 — Nada confiante(a)</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2 — Pouco confiante</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>significativo</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3 — Moderadamente confiante</t>
+          <t>Significativo</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>4 — Confiante</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -6588,12 +6638,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>5 — Muito confiante</t>
+          <t>1 — Nada confiante(a)</t>
         </is>
       </c>
     </row>
@@ -6605,80 +6655,80 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>2 — Pouco confiante</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>3 — Moderadamente confiante</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>material_didatico</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Material didático</t>
+          <t>4 — Confiante</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>tempo_de_planejamento</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tempo de planejamento</t>
+          <t>5 — Muito confiante</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6740,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -6707,12 +6757,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>material_didatico</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Material didático</t>
         </is>
       </c>
     </row>
@@ -6724,80 +6774,80 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>tempo_de_planejamento</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Tempo de planejamento</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>curriculo_sobrecarregado</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6859,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -6826,12 +6876,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>curriculo_sobrecarregado</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
@@ -6843,12 +6893,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>planejamento_coletivo</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6910,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>interdisciplinaridade</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6927,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>informacoes_territoriais</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6944,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>descontinuidade</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6961,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>rotatividade_de_profissionais</t>
+          <t>planejamento_coletivo</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -6928,148 +6978,148 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>interdisciplinaridade</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>informacoes_territoriais</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>descontinuidade</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>rotatividade_de_profissionais</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>livros_didaticos</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Livros didáticos</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>kits_cientificos</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Kits científicos</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -7081,12 +7131,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_escola</t>
+          <t>livros_didaticos</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Materiais produzidos pela escola</t>
+          <t>Livros didáticos</t>
         </is>
       </c>
     </row>
@@ -7098,12 +7148,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -7115,87 +7165,87 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>kits_cientificos</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Kits científicos</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>materiais_produzidos_pela_escola</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Materiais produzidos pela escola</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7212,75 +7262,75 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7297,153 +7347,153 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7505,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -7472,12 +7522,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>instituicao_parceira</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Instituição parceira</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -7489,182 +7539,182 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>instituicao_parceira</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Instituição parceira</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>assembleias</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Assembleias</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>projetos_protagonizados_por_estu</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Projetos protagonizados por estudantes</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>conselhos</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Conselhos</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -7676,267 +7726,267 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>assembleias</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Assembleias</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>projetos_protagonizados_por_estu</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Projetos protagonizados por estudantes</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>conselhos</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Conselhos</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7998,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -7965,12 +8015,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -7982,12 +8032,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -7999,12 +8049,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8066,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8083,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -8050,12 +8100,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -8067,12 +8117,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -8084,12 +8134,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8151,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -8118,12 +8168,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8185,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -8152,12 +8202,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8219,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -8186,12 +8236,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -8203,12 +8253,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -8220,12 +8270,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8287,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8304,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -8271,12 +8321,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -8288,12 +8338,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -8305,12 +8355,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -8322,12 +8372,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8389,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8406,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -8373,12 +8423,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -8390,12 +8440,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8457,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -8424,97 +8474,97 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -8526,250 +8576,250 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Não existe no território</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Não sei se existe</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>sem_contato</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Existe, mas nunca houve contato</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -8781,10 +8831,95 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
+          <t>nao_existe</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Não existe no território</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>nao_sei</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Não sei se existe</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>sem_contato</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Existe, mas nunca houve contato</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>contato_pontual</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>parceria</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Parceria — já colaboram em ações combinadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>nivel_rel_grade</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
           <t>articulacao</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C266" t="inlineStr">
         <is>
           <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
